--- a/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.5</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$87</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3243" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.7</t>
+    <t>1.1.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -509,6 +509,22 @@
   </si>
   <si>
     <t>Angir om legemidlet gis som en del av en klinisk studie.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:rekvirertVed</t>
+  </si>
+  <si>
+    <t>rekvirertVed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-rekvirert-ved}
+</t>
+  </si>
+  <si>
+    <t>Stedet (organisasjonen) rekvireringen ble utført</t>
+  </si>
+  <si>
+    <t>Rekvireringen refererer også til en episode, som igjen kan referere til en organisasjon. Rekvirert ved benyttes hvis episoden reflekterer hele innleggelsen, dvs. i tilfeller der episoden ikke gjenspeiler pasientens forflytninger (f.eks. mellom ulike avdelinger) under innleggelsen.</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -2270,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO86"/>
+  <dimension ref="A1:AO87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.53515625" customWidth="true" bestFit="true"/>
@@ -3719,48 +3735,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>163</v>
-      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3808,7 +3822,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3817,7 +3831,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>141</v>
@@ -3829,7 +3843,7 @@
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -3838,16 +3852,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3857,27 +3871,29 @@
         <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>81</v>
       </c>
@@ -3925,7 +3941,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3937,30 +3953,30 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3968,31 +3984,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4018,11 +4034,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4040,13 +4058,13 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
@@ -4055,27 +4073,27 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4083,31 +4101,31 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4133,13 +4151,11 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -4157,10 +4173,10 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>90</v>
@@ -4172,27 +4188,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4200,31 +4216,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4250,13 +4266,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -4274,10 +4290,10 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>90</v>
@@ -4289,27 +4305,27 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4317,31 +4333,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4367,13 +4383,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4391,13 +4407,13 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -4406,16 +4422,16 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4423,10 +4439,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4437,7 +4453,7 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
@@ -4446,18 +4462,20 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4482,13 +4500,13 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>81</v>
@@ -4506,13 +4524,13 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
@@ -4521,16 +4539,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4538,10 +4556,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4558,23 +4576,21 @@
         <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4599,13 +4615,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4623,7 +4639,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4638,16 +4654,16 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4655,10 +4671,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4675,13 +4691,13 @@
         <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>227</v>
@@ -4689,7 +4705,9 @@
       <c r="M21" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N21" s="2"/>
+      <c r="N21" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4738,7 +4756,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4759,7 +4777,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4768,12 +4786,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4781,13 +4799,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>81</v>
@@ -4796,7 +4814,7 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>232</v>
@@ -4804,9 +4822,7 @@
       <c r="M22" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4855,10 +4871,10 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>90</v>
@@ -4870,27 +4886,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>239</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4913,16 +4929,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4972,7 +4988,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>90</v>
@@ -4987,27 +5003,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>250</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5015,31 +5031,31 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5089,10 +5105,10 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -5104,27 +5120,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>182</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5135,7 +5151,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -5147,15 +5163,17 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5204,13 +5222,13 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -5219,27 +5237,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5250,7 +5268,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5259,16 +5277,16 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5319,13 +5337,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -5334,27 +5352,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5368,7 +5386,7 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>81</v>
@@ -5377,13 +5395,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5434,7 +5452,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5449,27 +5467,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AN27" t="s" s="2">
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5480,25 +5498,25 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5549,7 +5567,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5564,16 +5582,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5581,10 +5599,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5604,20 +5622,18 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>290</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5642,13 +5658,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5666,7 +5682,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5681,16 +5697,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5698,10 +5714,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5721,18 +5737,20 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5757,13 +5775,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5781,7 +5799,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5796,7 +5814,7 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
@@ -5805,7 +5823,7 @@
         <v>299</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5813,10 +5831,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5827,7 +5845,7 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -5839,7 +5857,7 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>186</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>302</v>
@@ -5847,9 +5865,7 @@
       <c r="M31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5874,13 +5890,13 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5898,13 +5914,13 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
@@ -5913,27 +5929,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5956,16 +5972,16 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>313</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5991,13 +6007,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -6015,7 +6031,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6030,27 +6046,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>182</v>
+        <v>313</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6070,18 +6086,20 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6130,7 +6148,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6145,16 +6163,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6162,10 +6180,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6188,7 +6206,7 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>104</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>326</v>
@@ -6245,7 +6263,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6260,13 +6278,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6277,10 +6295,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6291,7 +6309,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6303,13 +6321,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6360,7 +6378,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6375,13 +6393,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6392,10 +6410,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6406,7 +6424,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6418,7 +6436,7 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>334</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>335</v>
@@ -6427,9 +6445,7 @@
         <v>336</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>337</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6477,13 +6493,13 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
@@ -6492,13 +6508,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6509,10 +6525,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6532,21 +6548,21 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N37" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6570,13 +6586,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>345</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6594,7 +6610,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6609,13 +6625,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6626,10 +6642,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6640,7 +6656,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6652,15 +6668,17 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6685,13 +6703,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6709,13 +6727,13 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
@@ -6724,13 +6742,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6741,10 +6759,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6767,13 +6785,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6824,7 +6842,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6839,13 +6857,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6856,10 +6874,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6870,7 +6888,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6882,17 +6900,15 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6941,7 +6957,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6956,13 +6972,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6973,10 +6989,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6987,7 +7003,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6999,15 +7015,17 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7056,28 +7074,28 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -7088,21 +7106,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -7114,7 +7132,7 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>374</v>
@@ -7122,9 +7140,7 @@
       <c r="M42" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7161,40 +7177,40 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AD42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF42" t="s" s="2">
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7212,7 +7228,7 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7225,26 +7241,24 @@
         <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="N43" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7280,16 +7294,16 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>382</v>
@@ -7313,7 +7327,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7331,26 +7345,26 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>384</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>385</v>
@@ -7358,9 +7372,11 @@
       <c r="M44" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>387</v>
+        <v>168</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7409,19 +7425,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7430,21 +7446,21 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>389</v>
+        <v>133</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7455,7 +7471,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7467,17 +7483,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7526,7 +7542,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7547,21 +7563,21 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7572,7 +7588,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7584,19 +7600,17 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>186</v>
+        <v>373</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7621,13 +7635,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7645,13 +7659,13 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
@@ -7666,21 +7680,21 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7691,7 +7705,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7703,16 +7717,20 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>368</v>
+        <v>191</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7736,13 +7754,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7766,7 +7784,7 @@
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -7781,21 +7799,21 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7806,7 +7824,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7818,7 +7836,7 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>411</v>
+        <v>373</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>412</v>
@@ -7826,12 +7844,8 @@
       <c r="M48" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7879,7 +7893,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7900,21 +7914,21 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7937,18 +7951,20 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7972,13 +7988,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7996,7 +8012,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8017,21 +8033,21 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>427</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8054,20 +8070,18 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>186</v>
+        <v>424</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8091,13 +8105,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8115,7 +8129,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8136,21 +8150,21 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8173,17 +8187,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8208,13 +8224,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8232,7 +8248,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8253,21 +8269,21 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8290,19 +8306,17 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8327,13 +8341,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8351,7 +8365,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8372,21 +8386,21 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8397,7 +8411,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8409,16 +8423,20 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>458</v>
+        <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8442,13 +8460,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>458</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8466,13 +8484,13 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
@@ -8487,21 +8505,21 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>81</v>
+        <v>460</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8512,7 +8530,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8521,16 +8539,16 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>368</v>
+        <v>463</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>369</v>
+        <v>464</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>370</v>
+        <v>465</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8581,19 +8599,19 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>371</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -8602,32 +8620,32 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8639,7 +8657,7 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>135</v>
+        <v>373</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>374</v>
@@ -8647,9 +8665,7 @@
       <c r="M55" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N55" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8686,40 +8702,40 @@
         <v>81</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF55" t="s" s="2">
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8730,21 +8746,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8753,21 +8769,21 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>466</v>
+        <v>379</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8791,43 +8807,43 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>469</v>
+        <v>81</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>382</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -8836,21 +8852,21 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8873,19 +8889,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>474</v>
+        <v>191</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8910,13 +8924,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>81</v>
+        <v>474</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>81</v>
+        <v>475</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8934,7 +8948,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8955,21 +8969,21 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8992,19 +9006,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9053,7 +9067,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9074,21 +9088,21 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9111,19 +9125,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9172,7 +9186,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9193,21 +9207,21 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9230,19 +9244,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9291,7 +9305,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9312,21 +9326,21 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9349,17 +9363,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9408,7 +9424,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9429,7 +9445,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9454,7 +9470,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9463,19 +9479,21 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9523,7 +9541,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9541,10 +9559,10 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9555,10 +9573,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9569,7 +9587,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9581,13 +9599,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>368</v>
+        <v>518</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9638,7 +9656,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>371</v>
+        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9650,16 +9668,16 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>372</v>
+        <v>522</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9670,21 +9688,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9696,7 +9714,7 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>373</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>374</v>
@@ -9704,9 +9722,7 @@
       <c r="M64" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9755,28 +9771,28 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9787,14 +9803,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9807,26 +9823,24 @@
         <v>81</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="N65" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -9895,7 +9909,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9906,44 +9920,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>513</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>522</v>
+        <v>385</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>523</v>
+        <v>386</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9991,19 +10007,19 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>521</v>
+        <v>387</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -10012,7 +10028,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>525</v>
+        <v>133</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10049,15 +10065,17 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>368</v>
+        <v>518</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>369</v>
+        <v>527</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10106,7 +10124,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>371</v>
+        <v>526</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10118,7 +10136,7 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
@@ -10127,7 +10145,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>372</v>
+        <v>530</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10138,21 +10156,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10164,7 +10182,7 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>373</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>374</v>
@@ -10172,9 +10190,7 @@
       <c r="M68" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10223,28 +10239,28 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10255,14 +10271,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10275,26 +10291,24 @@
         <v>81</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="N69" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10363,7 +10377,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10374,42 +10388,46 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>500</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10457,19 +10475,19 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>529</v>
+        <v>387</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
@@ -10478,7 +10496,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>532</v>
+        <v>133</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10489,10 +10507,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10515,7 +10533,7 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>535</v>
@@ -10572,7 +10590,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10630,13 +10648,13 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10708,7 +10726,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10719,10 +10737,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10745,20 +10763,16 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N73" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="O73" t="s" s="2">
-        <v>546</v>
-      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10806,7 +10820,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10824,10 +10838,10 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>547</v>
+        <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -10838,10 +10852,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10864,18 +10878,20 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10923,7 +10939,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10941,24 +10957,24 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>556</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10981,15 +10997,17 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>500</v>
+        <v>555</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11038,7 +11056,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11056,24 +11074,24 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>562</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11096,17 +11114,15 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>566</v>
-      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11155,7 +11171,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11173,24 +11189,24 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11213,15 +11229,17 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11270,7 +11288,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11288,13 +11306,13 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>81</v>
+        <v>572</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>573</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11328,13 +11346,13 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>513</v>
+        <v>575</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11403,13 +11421,13 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>577</v>
+        <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>578</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
@@ -11443,13 +11461,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>368</v>
+        <v>518</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>369</v>
+        <v>580</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>370</v>
+        <v>581</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11500,7 +11518,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>371</v>
+        <v>579</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11512,16 +11530,16 @@
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>81</v>
+        <v>582</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>372</v>
+        <v>583</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11532,21 +11550,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>81</v>
@@ -11558,7 +11576,7 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>135</v>
+        <v>373</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>374</v>
@@ -11566,9 +11584,7 @@
       <c r="M80" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N80" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11617,28 +11633,28 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11649,14 +11665,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11669,26 +11685,24 @@
         <v>81</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="N81" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
       </c>
@@ -11757,7 +11771,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -11768,44 +11782,46 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>419</v>
+        <v>135</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>583</v>
+        <v>385</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>584</v>
+        <v>386</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
       </c>
@@ -11829,13 +11845,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>586</v>
+        <v>81</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>587</v>
+        <v>81</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -11853,42 +11869,42 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>582</v>
+        <v>387</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>577</v>
+        <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>588</v>
+        <v>133</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>589</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11896,7 +11912,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>90</v>
@@ -11911,15 +11927,17 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>186</v>
+        <v>424</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -11944,13 +11962,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -11968,10 +11986,10 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>90</v>
@@ -11986,24 +12004,24 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12026,13 +12044,13 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>599</v>
+        <v>191</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12059,13 +12077,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>81</v>
+        <v>598</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>81</v>
+        <v>599</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -12083,7 +12101,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12098,38 +12116,38 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>605</v>
+        <v>81</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12141,17 +12159,15 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>609</v>
-      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12200,13 +12216,13 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
@@ -12215,13 +12231,13 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>81</v>
+        <v>607</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>81</v>
+        <v>600</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -12232,14 +12248,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12258,16 +12274,16 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12317,7 +12333,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12332,23 +12348,140 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="AL86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM86" t="s" s="2">
+      <c r="B87" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K87" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="AN86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO86" t="s" s="2">
+      <c r="L87" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO86">
+  <autoFilter ref="A1:AO87">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12358,7 +12491,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI85">
+  <conditionalFormatting sqref="A2:AI86">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
